--- a/design/tables/MapPoint.xlsx
+++ b/design/tables/MapPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R09631ceeb672405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R2268add8efea4733"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -488,7 +488,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -1219,7 +1219,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1236,7 +1236,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -2256,7 +2256,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E116" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2273,7 +2273,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E117" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E124" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2409,7 +2409,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E125" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2528,7 +2528,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E132" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2545,7 +2545,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E133" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2664,7 +2664,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E140" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2681,7 +2681,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E141" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2800,7 +2800,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E148" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2817,7 +2817,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E149" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -3106,7 +3106,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E166" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -3123,7 +3123,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E167" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -3293,6 +3293,142 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E177" s="7" t="n">
+        <x:v>565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B178" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C178" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D178" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E178" t="n">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B179" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C179" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D179" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E179" t="n">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B180" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C180" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D180" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E180" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B181" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C181" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D181" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E181" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B182" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C182" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D182" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E182" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B183" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C183" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D183" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E183" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B184" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C184" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D184" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E184" t="n">
+        <x:v>565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B185" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C185" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D185" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E185" t="n">
         <x:v>565</x:v>
       </x:c>
     </x:row>

--- a/design/tables/MapPoint.xlsx
+++ b/design/tables/MapPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R2268add8efea4733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R686464ccd32f4739"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -522,7 +522,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -539,7 +539,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -706,7 +706,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>220</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
         <x:v>535</x:v>
@@ -723,7 +723,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>220</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
         <x:v>135</x:v>
@@ -794,7 +794,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -1576,7 +1576,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1593,7 +1593,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E77" s="7" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1763,7 +1763,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E87" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1882,7 +1882,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E94" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1899,7 +1899,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E95" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1916,7 +1916,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E96" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1933,7 +1933,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E97" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1950,7 +1950,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E98" s="7" t="n">
-        <x:v>425</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1967,7 +1967,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E99" s="7" t="n">
-        <x:v>425</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -2426,7 +2426,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E126" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2443,7 +2443,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E127" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2562,7 +2562,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E134" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2579,7 +2579,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E135" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -3004,7 +3004,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E160" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -3021,7 +3021,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E161" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -3140,7 +3140,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E168" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -3157,7 +3157,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E169" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -3310,7 +3310,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E178" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -3327,7 +3327,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E179" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="180">

--- a/design/tables/MapPoint.xlsx
+++ b/design/tables/MapPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R686464ccd32f4739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R3fbf5e29bb904f52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -386,7 +386,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -403,7 +403,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -420,7 +420,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -437,7 +437,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -454,7 +454,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -471,7 +471,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -488,7 +488,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -522,7 +522,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -539,7 +539,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -556,7 +556,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -573,7 +573,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -624,7 +624,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -641,7 +641,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -794,7 +794,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -828,7 +828,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -845,7 +845,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -862,7 +862,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -896,7 +896,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -913,7 +913,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -1100,7 +1100,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1117,7 +1117,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1134,7 +1134,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1151,7 +1151,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1168,7 +1168,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1185,7 +1185,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1202,7 +1202,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1219,7 +1219,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1236,7 +1236,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -1253,7 +1253,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E57" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1270,7 +1270,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E58" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1287,7 +1287,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1304,7 +1304,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1321,7 +1321,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1338,7 +1338,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1355,7 +1355,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E63" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1372,7 +1372,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E64" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1389,7 +1389,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E65" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1406,7 +1406,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1423,7 +1423,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1440,7 +1440,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1457,7 +1457,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1474,7 +1474,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E70" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1491,7 +1491,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E71" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1508,7 +1508,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E72" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1525,7 +1525,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E73" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1542,7 +1542,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E74" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1559,7 +1559,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E75" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1763,7 +1763,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E87" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1814,7 +1814,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E90" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1831,7 +1831,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E91" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1848,7 +1848,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E92" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1865,7 +1865,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E93" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1882,7 +1882,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E94" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1899,7 +1899,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E95" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1950,7 +1950,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E98" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1967,7 +1967,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E99" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E100" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -2001,7 +2001,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E101" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -2015,7 +2015,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D102" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E102" s="7" t="n">
         <x:v>185</x:v>
@@ -2032,7 +2032,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D103" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E103" s="7" t="n">
         <x:v>185</x:v>
@@ -2049,7 +2049,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D104" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E104" s="7" t="n">
         <x:v>535</x:v>
@@ -2066,7 +2066,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D105" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E105" s="7" t="n">
         <x:v>535</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E106" s="7" t="n">
         <x:v>135</x:v>
@@ -2100,7 +2100,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D107" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E107" s="7" t="n">
         <x:v>135</x:v>
@@ -2117,7 +2117,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D108" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E108" s="7" t="n">
         <x:v>435</x:v>
@@ -2134,7 +2134,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D109" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E109" s="7" t="n">
         <x:v>435</x:v>
@@ -2154,7 +2154,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E110" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -2171,7 +2171,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E111" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -2188,7 +2188,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E112" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -2205,7 +2205,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E113" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E114" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2239,7 +2239,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E115" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2256,7 +2256,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E116" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2273,7 +2273,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E117" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2290,7 +2290,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E118" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2307,7 +2307,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E119" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2324,7 +2324,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E120" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2341,7 +2341,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E121" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2358,7 +2358,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E122" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2375,7 +2375,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E123" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E124" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2409,7 +2409,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E125" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2426,7 +2426,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E126" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2443,7 +2443,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E127" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E128" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2477,7 +2477,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E129" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2494,7 +2494,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E130" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2511,7 +2511,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E131" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2528,7 +2528,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E132" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2545,7 +2545,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E133" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2562,7 +2562,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E134" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2579,7 +2579,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E135" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2596,7 +2596,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E136" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2613,7 +2613,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E137" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E138" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -2647,7 +2647,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E139" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2664,7 +2664,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E140" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2681,7 +2681,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E141" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E142" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2715,7 +2715,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E143" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2732,7 +2732,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E144" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -2749,7 +2749,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E145" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2766,7 +2766,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E146" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2783,7 +2783,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E147" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2800,7 +2800,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E148" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2817,7 +2817,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E149" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2831,10 +2831,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D150" s="7" t="n">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E150" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2848,10 +2848,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D151" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E151" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2865,7 +2865,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D152" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E152" s="7" t="n">
         <x:v>335</x:v>
@@ -2882,7 +2882,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D153" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E153" s="7" t="n">
         <x:v>335</x:v>
@@ -2899,10 +2899,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D154" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E154" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2916,10 +2916,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D155" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E155" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D156" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E156" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2950,10 +2950,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D157" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E157" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2967,10 +2967,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D158" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E158" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2984,10 +2984,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D159" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E159" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -3004,7 +3004,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E160" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -3021,7 +3021,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E161" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -3038,7 +3038,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E162" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -3055,7 +3055,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E163" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -3072,7 +3072,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E164" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -3089,7 +3089,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E165" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -3106,7 +3106,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E166" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -3123,7 +3123,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E167" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -3140,7 +3140,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E168" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -3157,7 +3157,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E169" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E170" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -3191,7 +3191,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E171" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -3208,7 +3208,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E172" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -3225,7 +3225,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E173" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -3242,7 +3242,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E174" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -3259,7 +3259,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E175" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -3276,7 +3276,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E176" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -3293,7 +3293,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E177" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="178">

--- a/design/tables/MapPoint.xlsx
+++ b/design/tables/MapPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="R3fbf5e29bb904f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="Rfa205145d9dd490a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -386,7 +386,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -403,7 +403,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -420,7 +420,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -437,7 +437,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -454,7 +454,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -471,7 +471,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -488,7 +488,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -522,7 +522,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -539,7 +539,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -556,7 +556,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>265</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -573,7 +573,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>265</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -624,7 +624,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -641,7 +641,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -658,7 +658,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E22" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -675,7 +675,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -760,7 +760,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -777,7 +777,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -794,7 +794,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>180</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>180</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -828,7 +828,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -845,7 +845,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -862,7 +862,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>400</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>400</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -896,7 +896,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -913,7 +913,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -930,7 +930,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E38" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -947,7 +947,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E39" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -1066,7 +1066,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1083,7 +1083,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1100,7 +1100,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>140</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1117,7 +1117,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1134,7 +1134,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1151,7 +1151,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1168,7 +1168,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1185,7 +1185,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1202,7 +1202,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1219,7 +1219,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1236,7 +1236,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -1253,7 +1253,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E57" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1270,7 +1270,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E58" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1287,7 +1287,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1304,7 +1304,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1321,7 +1321,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1338,7 +1338,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1355,7 +1355,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E63" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1372,7 +1372,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E64" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1389,7 +1389,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E65" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1406,7 +1406,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1423,7 +1423,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
-        <x:v>140</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1440,7 +1440,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1457,7 +1457,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1474,7 +1474,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E70" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1491,7 +1491,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E71" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1508,7 +1508,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E72" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1525,7 +1525,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E73" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1542,7 +1542,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E74" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1559,7 +1559,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E75" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1712,7 +1712,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E84" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1729,7 +1729,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E85" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1763,7 +1763,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E87" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1814,7 +1814,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E90" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1831,7 +1831,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E91" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1882,7 +1882,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E94" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1899,7 +1899,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E95" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1950,7 +1950,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E98" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1967,7 +1967,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E99" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -2015,7 +2015,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D102" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E102" s="7" t="n">
         <x:v>185</x:v>
@@ -2032,7 +2032,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D103" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E103" s="7" t="n">
         <x:v>185</x:v>
@@ -2049,7 +2049,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D104" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E104" s="7" t="n">
         <x:v>535</x:v>
@@ -2066,7 +2066,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D105" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E105" s="7" t="n">
         <x:v>535</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E106" s="7" t="n">
         <x:v>135</x:v>
@@ -2100,7 +2100,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D107" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E107" s="7" t="n">
         <x:v>135</x:v>
@@ -2117,7 +2117,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D108" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E108" s="7" t="n">
         <x:v>435</x:v>
@@ -2134,7 +2134,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D109" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E109" s="7" t="n">
         <x:v>435</x:v>
@@ -2154,7 +2154,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E110" s="7" t="n">
-        <x:v>160</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -2171,7 +2171,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E111" s="7" t="n">
-        <x:v>160</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -2188,7 +2188,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E112" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -2205,7 +2205,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E113" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E114" s="7" t="n">
-        <x:v>400</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2239,7 +2239,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E115" s="7" t="n">
-        <x:v>400</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2256,7 +2256,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E116" s="7" t="n">
-        <x:v>500</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2273,7 +2273,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E117" s="7" t="n">
-        <x:v>500</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2290,7 +2290,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E118" s="7" t="n">
-        <x:v>175</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2307,7 +2307,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E119" s="7" t="n">
-        <x:v>175</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2324,7 +2324,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E120" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2341,7 +2341,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E121" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2358,7 +2358,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E122" s="7" t="n">
-        <x:v>395</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2375,7 +2375,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E123" s="7" t="n">
-        <x:v>395</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E124" s="7" t="n">
-        <x:v>495</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2409,7 +2409,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E125" s="7" t="n">
-        <x:v>495</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2426,7 +2426,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E126" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2443,7 +2443,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E127" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E128" s="7" t="n">
-        <x:v>270</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2477,7 +2477,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E129" s="7" t="n">
-        <x:v>270</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2494,7 +2494,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E130" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2511,7 +2511,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E131" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2528,7 +2528,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E132" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2545,7 +2545,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E133" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2562,7 +2562,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E134" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2579,7 +2579,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E135" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2596,7 +2596,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E136" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2613,7 +2613,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E137" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E138" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -2647,7 +2647,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E139" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2664,7 +2664,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E140" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2681,7 +2681,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E141" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E142" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2715,7 +2715,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E143" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2732,7 +2732,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E144" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -2749,7 +2749,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E145" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2766,7 +2766,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E146" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2783,7 +2783,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E147" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2800,7 +2800,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E148" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2817,7 +2817,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E149" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2831,10 +2831,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D150" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E150" s="7" t="n">
-        <x:v>155</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2848,10 +2848,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D151" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E151" s="7" t="n">
-        <x:v>155</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2865,10 +2865,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D152" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E152" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2882,10 +2882,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D153" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E153" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2899,10 +2899,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D154" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E154" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2916,10 +2916,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D155" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E155" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D156" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E156" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2950,10 +2950,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D157" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E157" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2967,10 +2967,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D158" s="7" t="n">
-        <x:v>110</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E158" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2984,10 +2984,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D159" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E159" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -3004,7 +3004,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E160" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -3021,7 +3021,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E161" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -3038,7 +3038,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E162" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -3055,7 +3055,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E163" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -3072,7 +3072,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E164" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -3089,7 +3089,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E165" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -3106,7 +3106,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E166" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -3123,7 +3123,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="E167" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -3140,7 +3140,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E168" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -3157,7 +3157,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E169" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E170" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -3191,7 +3191,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E171" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -3208,7 +3208,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E172" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -3225,7 +3225,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E173" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -3242,7 +3242,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E174" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -3259,7 +3259,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E175" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -3276,7 +3276,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E176" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -3293,7 +3293,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E177" s="7" t="n">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="178">

--- a/design/tables/MapPoint.xlsx
+++ b/design/tables/MapPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="Rfa205145d9dd490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPoint" sheetId="1" r:id="Rb6e1fc5484a84c16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3432,6 +3432,1434 @@
         <x:v>565</x:v>
       </x:c>
     </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="7" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="B186" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C186" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D186" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E186" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="7" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="B187" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C187" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D187" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E187" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="7" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="B188" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C188" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D188" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E188" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="7" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="B189" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C189" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D189" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E189" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="7" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="B190" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C190" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D190" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E190" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="7" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="B191" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C191" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D191" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E191" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="7" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="B192" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C192" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D192" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E192" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="7" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="B193" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C193" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D193" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E193" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="7" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="B194" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C194" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D194" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E194" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="7" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="B195" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C195" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D195" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E195" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="7" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="B196" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C196" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D196" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E196" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="7" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="B197" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C197" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D197" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E197" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="7" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="B198" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C198" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D198" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E198" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="7" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="B199" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C199" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D199" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E199" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="7" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="B200" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C200" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D200" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E200" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="7" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="B201" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C201" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D201" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E201" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="7" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="B202" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C202" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D202" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E202" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="7" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="B203" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C203" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D203" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E203" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="7" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="B204" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C204" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D204" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E204" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="7" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="B205" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C205" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D205" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E205" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="7" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="B206" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C206" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D206" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E206" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="7" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="B207" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C207" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D207" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E207" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="7" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="B208" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C208" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D208" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E208" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="7" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="B209" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C209" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D209" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E209" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="7" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="B210" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C210" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D210" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E210" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="7" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="B211" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C211" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D211" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E211" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="7" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="B212" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C212" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D212" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E212" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="7" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="B213" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C213" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D213" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E213" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="7" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="B214" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C214" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D214" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E214" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="7" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="B215" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C215" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D215" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E215" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="7" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="B216" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C216" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D216" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E216" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="7" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="B217" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C217" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D217" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E217" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="7" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="B218" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C218" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D218" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E218" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="7" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="B219" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C219" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D219" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E219" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="7" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="B220" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C220" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D220" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E220" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="7" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="B221" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C221" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D221" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E221" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="7" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="B222" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C222" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D222" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E222" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="7" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B223" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C223" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D223" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E223" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="7" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="B224" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C224" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D224" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E224" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="7" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="B225" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C225" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D225" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E225" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="7" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="B226" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C226" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D226" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E226" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="7" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B227" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C227" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D227" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E227" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="7" t="n">
+        <x:v>2701</x:v>
+      </x:c>
+      <x:c r="B228" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C228" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D228" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E228" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="7" t="n">
+        <x:v>2702</x:v>
+      </x:c>
+      <x:c r="B229" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C229" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D229" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E229" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="7" t="n">
+        <x:v>2703</x:v>
+      </x:c>
+      <x:c r="B230" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C230" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D230" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E230" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="7" t="n">
+        <x:v>2704</x:v>
+      </x:c>
+      <x:c r="B231" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C231" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D231" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E231" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="7" t="n">
+        <x:v>2705</x:v>
+      </x:c>
+      <x:c r="B232" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C232" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D232" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E232" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="7" t="n">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="B233" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C233" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D233" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E233" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="7" t="n">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="B234" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C234" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D234" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E234" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="7" t="n">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="B235" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C235" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D235" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E235" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="7" t="n">
+        <x:v>2801</x:v>
+      </x:c>
+      <x:c r="B236" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C236" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D236" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E236" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="7" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="B237" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C237" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D237" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E237" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="7" t="n">
+        <x:v>2803</x:v>
+      </x:c>
+      <x:c r="B238" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C238" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D238" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E238" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="7" t="n">
+        <x:v>2804</x:v>
+      </x:c>
+      <x:c r="B239" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C239" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D239" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E239" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="7" t="n">
+        <x:v>2805</x:v>
+      </x:c>
+      <x:c r="B240" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C240" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D240" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E240" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="7" t="n">
+        <x:v>2806</x:v>
+      </x:c>
+      <x:c r="B241" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C241" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D241" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E241" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="7" t="n">
+        <x:v>2807</x:v>
+      </x:c>
+      <x:c r="B242" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C242" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D242" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E242" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="7" t="n">
+        <x:v>2808</x:v>
+      </x:c>
+      <x:c r="B243" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C243" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D243" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E243" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="7" t="n">
+        <x:v>2901</x:v>
+      </x:c>
+      <x:c r="B244" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C244" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D244" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E244" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="7" t="n">
+        <x:v>2902</x:v>
+      </x:c>
+      <x:c r="B245" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C245" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D245" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E245" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="7" t="n">
+        <x:v>2903</x:v>
+      </x:c>
+      <x:c r="B246" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C246" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D246" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E246" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="7" t="n">
+        <x:v>2904</x:v>
+      </x:c>
+      <x:c r="B247" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C247" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D247" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E247" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="7" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="B248" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C248" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D248" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E248" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="7" t="n">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="B249" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C249" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D249" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E249" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="7" t="n">
+        <x:v>2907</x:v>
+      </x:c>
+      <x:c r="B250" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C250" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D250" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E250" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="7" t="n">
+        <x:v>2908</x:v>
+      </x:c>
+      <x:c r="B251" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C251" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D251" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E251" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="7" t="n">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="B252" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C252" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D252" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E252" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="7" t="n">
+        <x:v>3002</x:v>
+      </x:c>
+      <x:c r="B253" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C253" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D253" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E253" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="7" t="n">
+        <x:v>3003</x:v>
+      </x:c>
+      <x:c r="B254" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C254" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D254" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E254" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="7" t="n">
+        <x:v>3004</x:v>
+      </x:c>
+      <x:c r="B255" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C255" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D255" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E255" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="7" t="n">
+        <x:v>3005</x:v>
+      </x:c>
+      <x:c r="B256" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C256" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D256" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E256" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="7" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="B257" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C257" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D257" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E257" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="7" t="n">
+        <x:v>3007</x:v>
+      </x:c>
+      <x:c r="B258" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C258" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D258" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E258" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="7" t="n">
+        <x:v>3008</x:v>
+      </x:c>
+      <x:c r="B259" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C259" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D259" s="7" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E259" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="7" t="n">
+        <x:v>3101</x:v>
+      </x:c>
+      <x:c r="B260" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C260" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D260" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E260" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="7" t="n">
+        <x:v>3102</x:v>
+      </x:c>
+      <x:c r="B261" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C261" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D261" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E261" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="7" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="B262" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C262" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D262" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E262" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="7" t="n">
+        <x:v>3104</x:v>
+      </x:c>
+      <x:c r="B263" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C263" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D263" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E263" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="7" t="n">
+        <x:v>3105</x:v>
+      </x:c>
+      <x:c r="B264" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C264" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D264" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E264" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="7" t="n">
+        <x:v>3106</x:v>
+      </x:c>
+      <x:c r="B265" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C265" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D265" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E265" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="7" t="n">
+        <x:v>3107</x:v>
+      </x:c>
+      <x:c r="B266" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C266" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D266" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E266" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="7" t="n">
+        <x:v>3108</x:v>
+      </x:c>
+      <x:c r="B267" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C267" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D267" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E267" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="7" t="n">
+        <x:v>3109</x:v>
+      </x:c>
+      <x:c r="B268" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C268" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D268" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E268" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="7" t="n">
+        <x:v>3110</x:v>
+      </x:c>
+      <x:c r="B269" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C269" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D269" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E269" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
